--- a/proformas-concurrentes/Tableau_Comparatif_Offres_ANMC.xlsx
+++ b/proformas-concurrentes/Tableau_Comparatif_Offres_ANMC.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Comparatif des 3 Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Comparatif des 3 Offres'!$A$1:$G$21</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -32,33 +34,33 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F4E79"/>
-      <sz val="15"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00595959"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00000000"/>
-      <sz val="9.5"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +77,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F9"/>
+        <bgColor rgb="00F2F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,6 +109,12 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
       <top style="medium">
         <color rgb="001F4E79"/>
       </top>
@@ -112,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +150,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -530,35 +556,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLEAU COMPARATIF D'ANALYSE DES OFFRES FINANCIÈRES — FOURNITURE ÉTIQUETTES &amp; SCELLÉS ANMC</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TABLEAU COMPARATIF D'ANALYSE DES OFFRES FINANCIÈRES — ANMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Dossier de consultation / Procédure de mise en concurrence à 3 devis contradictoires (Réf. Client : NIF 82397/P)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>N°</t>
@@ -582,7 +609,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Offre 2 : Imprimerie IMS SARL
+          <t>Offre 2 : IMS SARL
 (Facture A : +30%)</t>
         </is>
       </c>
@@ -599,7 +626,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="17" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -625,33 +652,33 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Étiquette verte 9cm X 9cm (2028, n°0001 à 8000)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="11" t="n">
         <v>8000</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>1200000</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="11" t="n">
         <v>1560000</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="11" t="n">
         <v>1600000</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="12">
         <f>F6-D6</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="17" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
@@ -677,33 +704,33 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Étiquette rouge 9cm X 9cm (n°3001 à 4000)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>150000</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="11" t="n">
         <v>195000</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="11" t="n">
         <v>200000</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="12">
         <f>F8-D8</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="17" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
@@ -729,33 +756,33 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Étiquette verte 5,5cm X 5,5cm (2028, n°0001 à 1000)</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>100000</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="11" t="n">
         <v>130000</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="11" t="n">
         <v>140000</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="12">
         <f>F10-D10</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="17" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
@@ -781,33 +808,33 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Étiquette rouge 5,5cm X 5,5cm (n°2001 à 3000)</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="11" t="n">
         <v>1000</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>100000</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="11" t="n">
         <v>130000</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="11" t="n">
         <v>140000</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="12">
         <f>F12-D12</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="17" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
@@ -833,33 +860,33 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Étiquette verte 5cm X 2cm (2028, n°1 à 250)</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="11" t="n">
         <v>250</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>22500</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="11" t="n">
         <v>29250</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="11" t="n">
         <v>30000</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="12">
         <f>F14-D14</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="17" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
@@ -885,83 +912,83 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL MONTANT HORS TAXES (HT)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="11">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL MONTANT HORS TAXES (HT) FCFA</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="15">
         <f>SUM(D5:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="16">
         <f>SUM(E5:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="16">
         <f>SUM(F5:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="17">
         <f>F16-D16</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Écart en % vs Offre Moins-Disante</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>RÉFÉRENCE (0%)</t>
         </is>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="20">
         <f>(E16-D16)/D16</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="20">
         <f>(F16-D16)/D16</f>
         <v/>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>Économie ANMC</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>CONCLUSION DE L'ÉVALUATION FINANCIÈRE :</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>L'offre soumise par Niger CERTIFY d'un montant de 3 645 000 FCFA HT est l'offre la moins-disante et la plus avantageuse pour l'ANMC.
-Elle présente une économie de 1 093 500 FCFA (-23,1%) par rapport à l'Offre A (IMS SARL) et de 1 275 000 FCFA (-25,9%) par rapport à l'Offre B (SGSI SA).
-Recommandation : Attribution définitive du marché de confection des étiquettes et scellés à Niger CERTIFY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
+    <row r="18" ht="6" customHeight="1"/>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>CONCLUSION &amp; RECOMMANDATION D'ATTRIBUTION :</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>L'offre soumise par Niger CERTIFY d'un montant de 3 645 000 FCFA HT est l'offre la moins-disante et la plus avantageuse pour l'ANMC. Elle dégage une économie de 1 093 500 FCFA (-23,1%) par rapport à l'Offre A (IMS SARL) et de 1 275 000 FCFA (-25,9%) par rapport à l'Offre B (SGSI SA). Recommandation : Attribution définitive du marché à Niger CERTIFY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A20:G22"/>
+    <mergeCell ref="A20:G21"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A16:C16"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" gridLines="0"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>